--- a/docs/NigerCertify-Calendrier-Publication.xlsx
+++ b/docs/NigerCertify-Calendrier-Publication.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarifs_offres" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Calendrier'!$A$1:$M$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Calendrier'!$A$1:$N$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -130,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -142,6 +146,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -163,7 +170,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -532,25 +539,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Semaine</t>
@@ -578,46 +586,51 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Titre / Accroche</t>
+          <t>Titre</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Texte / Script (brouillon)</t>
+          <t>Contenu</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Hashtags</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>CTA / Mot-clé</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Statut</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Lien publication</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -641,37 +654,49 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Session PECB 10 oct. 2026 — inscriptions ouvertes</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>ISO 27001 · ISO 27701 · en ligne · 12 mois · 2 retakes · 350 000 FCFA
-WhatsApp 94 10 70 74 — JE M’INSCRIS</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Post carrousel / texte</t>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Session PECB — inscriptions ouvertes (10 oct. 2026)</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Les inscriptions sont ouvertes pour la session PECB NigerCertify.
+📅 Démarrage : 10 octobre 2026
+💻 100 % en ligne
+📘 ISO/IEC 27001 · ISO/IEC 27701
+⏱ Accès plateforme 12 mois
+🔁 2 retakes examens inclus
+💰 Tarif : 350 000 FCFA
+Niger &amp; Sénégal — certification internationale, accompagnement local.
+👉 WhatsApp 94 10 70 74 — écrivez JE M’INSCRIS</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>#PECB #ISO27001 #ISO27701 #Cybersécurité #Certification #NigerCertify #Niger #Sénégal #FormationEnLigne</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>Post texte / carrousel</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
+      <c r="N2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="90" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
@@ -685,46 +710,56 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Parcours LPI : LE → LPIC-1 → LPIC-2 → LPIC-3</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Format mixte. LE 150 000 FCFA · LPIC 200 000 FCFA / niveau.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Parcours LPI : de Linux Essentials à LPIC-3</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Admin Linux : un chemin clair avec NigerCertify.
+🐧 LPI LE (Linux Essentials) — 150 000 FCFA
+🐧 LPIC-1 · LPIC-2 · LPIC-3 — 200 000 FCFA / niveau
+📍 Format mixte (présentiel + en ligne)
+Progression : LE → LPIC-1 → LPIC-2 → LPIC-3
+Répondez LPI au 94 10 70 74 + votre niveau</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>#LPI #LPIC #Linux #LinuxEssentials #SysAdmin #NigerCertify #FormationLinux #OpenSource</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Post image + texte</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="N3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4" ht="90" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>1</v>
       </c>
@@ -748,36 +783,47 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Pourquoi ISO 27001 ?</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Le langage commun de la sécurité de l’information. Session PECB NigerCertify dès le 10/10/2026.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Pourquoi se certifier ISO 27001 ?</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>ISO 27001, c’est le langage commun de la sécurité de l’information.
+Avec NigerCertify, vous préparez votre certification PECB :
+• Session en ligne dès le 10 octobre 2026
+• Accès 12 mois + 2 retakes
+• Tarif : 350 000 FCFA
+Idéal pour RSSI, IT, consultants et équipes conformité.
+📩 Demandez le programme au 94 10 70 74 (mot-clé PROGRAMME)</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>#ISO27001 #PECB #SécuritéDeLInformation #SMSI #FormationIT #NigerCertify #AfriqueDeLOuest</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Post texte + CTA</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>PROGRAMME</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
+      <c r="N4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="90" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>1</v>
       </c>
@@ -801,40 +847,55 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Ce qui est inclus pour 350 000 FCFA</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>TITRE : Ce qui est inclus pour 350 000 FCFA
-HOOK (0–5s) : Ce qui est inclus pour 350 000 FCFA
-CORPS : Formation PECB + accès 12 mois + examen + 2 retakes + suivi NigerCertify.
-CTA fin : Écrivez PECB au 94 10 70 74
-DESCRIPTION : NigerCertify · Niger &amp; Sénégal · https://wa.me/22794107074?text=PECB</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>350 000 FCFA : ce qui est vraiment inclus</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>TITRE VIDÉO : 350 000 FCFA : ce qui est vraiment inclus
+HOOK (0–5 s) : 350 000 FCFA : ce qui est vraiment inclus
+SCRIPT / CONTENU :
+Pour 350 000 FCFA, la session PECB du 10/10/2026 inclut :
+✅ Formation PECB (ISO 27001 / 27701)
+✅ Accès en ligne 12 mois
+✅ Passage d’examen + 2 retakes
+✅ Accompagnement NigerCertify
+Pas de surprise. Un parcours clair pour réussir.
+WhatsApp 94 10 70 74 — répondez PECB
+CTA ÉCRAN DE FIN : Écrivez PECB au 94 10 70 74
+DESCRIPTION YOUTUBE :
+Pour 350 000 FCFA, la session PECB du 10/10/2026 inclut :
+WhatsApp : https://wa.me/22794107074?text=PECB
+NigerCertify · Niger &amp; Sénégal</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>#PECB #Formation #ISO27001 #ISO27701 #CertificationPro #NigerCertify #InvestissementFormation</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Vidéo 5–8 min</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>PECB</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="N5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>1</v>
       </c>
@@ -848,46 +909,57 @@
           <t>Ven</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>nBusiness</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>nBusiness — gestion multi-secteur</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Commerce, école, pressing, business : stock, clients, ventes.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>nBusiness — la gestion multi-secteur</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Commerce, école, pressing, business…
+nBusiness centralise :
+• Stocks
+• Clients
+• Ventes
+Sans usine à gaz. Pensé pour les PME du Niger et du Sénégal.
+Démo 10 min : écrivez NBUSINESS au 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>#nBusiness #GestionPME #Digitalisation #Commerce #Pressing #Éducation #NigerCertify #PME</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Post / Reels</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>NBUSINESS</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
+      <c r="N6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="90" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>1</v>
       </c>
@@ -911,36 +983,45 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>ISO 27701 — privacy</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Protéger les données personnelles : extension naturelle du SMSI. Places session 10 oct.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Statut / CTA session</t>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>ISO 27701 : la privacy au cœur du SMSI</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Protéger les données personnelles n’est plus optionnel.
+ISO/IEC 27701 complète ISO 27001 pour structurer la privacy.
+Session PECB NigerCertify — démarrage 10 octobre 2026
+En ligne · 12 mois · 2 retakes · 350 000 FCFA
+Places limitées → 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>#ISO27701 #Privacy #ProtectionDesDonnées #RGPD #PECB #NigerCertify #Conformité</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>Post CTA session</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>PROGRAMME</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
+      <c r="N7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>2</v>
       </c>
@@ -964,36 +1045,46 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Niger &amp; Sénégal — même session en ligne</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Certification internationale, accompagnement local. 94 10 70 74</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Post carrousel / texte</t>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Niamey ↔ Dakar : une même session en ligne</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Que vous soyez au Niger ou au Sénégal, la session PECB est la même :
+• Exigence internationale
+• Accompagnement local NigerCertify
+• Démarrage 10 octobre 2026
+• 350 000 FCFA · 2 retakes
+Inscrivez-vous : WhatsApp 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>#Niger #Sénégal #PECB #FormationEnLigne #ISO27001 #NigerCertify #Certification</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>Post texte / carrousel</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="N8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="90" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>2</v>
       </c>
@@ -1007,46 +1098,57 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Linux Essentials — premier pas</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>LPI LE · 150 000 FCFA · mixte. Idéal débutants &amp; reconversion.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Linux Essentials — le bon premier pas</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Vous débutez sous Linux ou vous vous reconvertissez en IT ?
+LPI Linux Essentials (LPI LE) chez NigerCertify :
+• Bases système &amp; ligne de commande
+• Culture open source
+• Tarif : 150 000 FCFA
+• Format mixte
+Message LPI LE au 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>#LinuxEssentials #LPILE #Linux #ReconversionIT #Formation #NigerCertify #LPIC</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Post image + texte</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>LPI LE</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
+      <c r="N9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>2</v>
       </c>
@@ -1070,37 +1172,49 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Session PECB 10 oct. 2026 — inscriptions ouvertes</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>ISO 27001 · ISO 27701 · en ligne · 12 mois · 2 retakes · 350 000 FCFA
-WhatsApp 94 10 70 74 — JE M’INSCRIS</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Session PECB — inscriptions ouvertes (10 oct. 2026)</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Les inscriptions sont ouvertes pour la session PECB NigerCertify.
+📅 Démarrage : 10 octobre 2026
+💻 100 % en ligne
+📘 ISO/IEC 27001 · ISO/IEC 27701
+⏱ Accès plateforme 12 mois
+🔁 2 retakes examens inclus
+💰 Tarif : 350 000 FCFA
+Niger &amp; Sénégal — certification internationale, accompagnement local.
+👉 WhatsApp 94 10 70 74 — écrivez JE M’INSCRIS</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>#PECB #ISO27001 #ISO27701 #Cybersécurité #Certification #NigerCertify #Niger #Sénégal #FormationEnLigne</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Post texte + CTA</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
+      <c r="N10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="90" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>2</v>
       </c>
@@ -1114,50 +1228,65 @@
           <t>Jeu</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>LPIC-1 / 2 / 3 — montez en niveau</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>TITRE : LPIC-1 / 2 / 3 — montez en niveau
-HOOK (0–5s) : LPIC-1 / 2 / 3 — montez en niveau
-CORPS : Admin → Engineer → Enterprise. 200 000 FCFA / niveau · format mixte.
-CTA fin : Écrivez LPI au 94 10 70 74
-DESCRIPTION : NigerCertify · Niger &amp; Sénégal · https://wa.me/22794107074?text=LPI</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>LPIC-1, LPIC-2, LPIC-3 : montez en niveau</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>TITRE VIDÉO : LPIC-1, LPIC-2, LPIC-3 : montez en niveau
+HOOK (0–5 s) : LPIC-1, LPIC-2, LPIC-3 : montez en niveau
+SCRIPT / CONTENU :
+Déjà à l’aise sous Linux ? Passez au niveau supérieur.
+• LPIC-1 — Administrateur
+• LPIC-2 — Engineer
+• LPIC-3 — Enterprise
+Tarif : 200 000 FCFA / niveau · Format mixte
+NigerCertify — Niger &amp; Sénégal
+WhatsApp 94 10 70 74 — mot-clé LPI
+CTA ÉCRAN DE FIN : Écrivez LPI au 94 10 70 74
+DESCRIPTION YOUTUBE :
+Déjà à l’aise sous Linux ? Passez au niveau supérieur.
+WhatsApp : https://wa.me/22794107074?text=LPI
+NigerCertify · Niger &amp; Sénégal</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>#LPIC1 #LPIC2 #LPIC3 #LinuxAdmin #DevOps #NigerCertify #CertificationLinux</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Vidéo 5–8 min</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="N11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>2</v>
       </c>
@@ -1171,46 +1300,54 @@
           <t>Ven</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>nBusiness</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Démo nBusiness 10 min</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Réservez une démo WhatsApp. 94 10 70 74</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Démo nBusiness en 10 minutes</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Envie de voir nBusiness en action ?
+On vous montre en 10 minutes sur WhatsApp comment suivre stock, clients et ventes.
+Idéal commerce, école, pressing et business.
+Réservez : 94 10 70 74 — mot-clé NBUSINESS</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>#nBusiness #DémoLogiciel #PME #GestionCommerciale #Niger #Sénégal #NigerCertify</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Post / Reels</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>NBUSINESS</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
+      <c r="N12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="90" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>2</v>
       </c>
@@ -1234,36 +1371,47 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Pourquoi ISO 27001 ?</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Le langage commun de la sécurité de l’information. Session PECB NigerCertify dès le 10/10/2026.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Statut / CTA session</t>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Pourquoi se certifier ISO 27001 ?</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>ISO 27001, c’est le langage commun de la sécurité de l’information.
+Avec NigerCertify, vous préparez votre certification PECB :
+• Session en ligne dès le 10 octobre 2026
+• Accès 12 mois + 2 retakes
+• Tarif : 350 000 FCFA
+Idéal pour RSSI, IT, consultants et équipes conformité.
+📩 Demandez le programme au 94 10 70 74 (mot-clé PROGRAMME)</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>#ISO27001 #PECB #SécuritéDeLInformation #SMSI #FormationIT #NigerCertify #AfriqueDeLOuest</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>Post CTA session</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>PROGRAMME</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
+      <c r="N13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>3</v>
       </c>
@@ -1287,36 +1435,47 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Ce qui est inclus pour 350 000 FCFA</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Formation PECB + accès 12 mois + examen + 2 retakes + suivi NigerCertify.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Post carrousel / texte</t>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>350 000 FCFA : ce qui est vraiment inclus</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Pour 350 000 FCFA, la session PECB du 10/10/2026 inclut :
+✅ Formation PECB (ISO 27001 / 27701)
+✅ Accès en ligne 12 mois
+✅ Passage d’examen + 2 retakes
+✅ Accompagnement NigerCertify
+Pas de surprise. Un parcours clair pour réussir.
+WhatsApp 94 10 70 74 — répondez PECB</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>#PECB #Formation #ISO27001 #ISO27701 #CertificationPro #NigerCertify #InvestissementFormation</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>Post texte / carrousel</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>PECB</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
+      <c r="N14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="90" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>3</v>
       </c>
@@ -1330,46 +1489,56 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Tip Linux (60 sec)</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Une commande utile + lien vers le parcours LPI NigerCertify.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Tip Linux : une commande, un métier</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Maîtriser Linux, c’est maîtriser le terrain IT.
+Chaque semaine, NigerCertify vous prépare aux certifications LPI :
+LE (150 000 FCFA) · LPIC-1/2/3 (200 000 FCFA) · format mixte.
+Aujourd’hui : prenez 10 minutes pour réviser une commande.
+Demain : visez la certif.
+Écrivez LPI au 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>#LinuxTip #LPI #SysAdmin #Terminal #OpenSource #NigerCertify #FormationIT</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Post image + texte</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
+      <c r="N15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="90" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>3</v>
       </c>
@@ -1393,36 +1562,45 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>ISO 27701 — privacy</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Protéger les données personnelles : extension naturelle du SMSI. Places session 10 oct.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>ISO 27701 : la privacy au cœur du SMSI</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Protéger les données personnelles n’est plus optionnel.
+ISO/IEC 27701 complète ISO 27001 pour structurer la privacy.
+Session PECB NigerCertify — démarrage 10 octobre 2026
+En ligne · 12 mois · 2 retakes · 350 000 FCFA
+Places limitées → 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>#ISO27701 #Privacy #ProtectionDesDonnées #RGPD #PECB #NigerCertify #Conformité</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Post texte + CTA</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>PROGRAMME</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
+      <c r="N16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="90" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>3</v>
       </c>
@@ -1446,40 +1624,54 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Niger &amp; Sénégal — même session en ligne</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>TITRE : Niger &amp; Sénégal — même session en ligne
-HOOK (0–5s) : Niger &amp; Sénégal — même session en ligne
-CORPS : Certification internationale, accompagnement local. 94 10 70 74
-CTA fin : Écrivez JE M’INSCRIS au 94 10 70 74
-DESCRIPTION : NigerCertify · Niger &amp; Sénégal · https://wa.me/22794107074?text=JE%20M’INSCRIS</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Niamey ↔ Dakar : une même session en ligne</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>TITRE VIDÉO : Niamey ↔ Dakar : une même session en ligne
+HOOK (0–5 s) : Niamey ↔ Dakar : une même session en ligne
+SCRIPT / CONTENU :
+Que vous soyez au Niger ou au Sénégal, la session PECB est la même :
+• Exigence internationale
+• Accompagnement local NigerCertify
+• Démarrage 10 octobre 2026
+• 350 000 FCFA · 2 retakes
+Inscrivez-vous : WhatsApp 94 10 70 74
+CTA ÉCRAN DE FIN : Écrivez JE M’INSCRIS au 94 10 70 74
+DESCRIPTION YOUTUBE :
+Que vous soyez au Niger ou au Sénégal, la session PECB est la même :
+WhatsApp : https://wa.me/22794107074?text=JE%20M’INSCRIS
+NigerCertify · Niger &amp; Sénégal</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>#Niger #Sénégal #PECB #FormationEnLigne #ISO27001 #NigerCertify #Certification</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>YouTube Short (45–60s)</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
+      <c r="N17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="90" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>3</v>
       </c>
@@ -1493,46 +1685,57 @@
           <t>Ven</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>nBusiness</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>nBusiness — gestion multi-secteur</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Commerce, école, pressing, business : stock, clients, ventes.</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>nBusiness — la gestion multi-secteur</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Commerce, école, pressing, business…
+nBusiness centralise :
+• Stocks
+• Clients
+• Ventes
+Sans usine à gaz. Pensé pour les PME du Niger et du Sénégal.
+Démo 10 min : écrivez NBUSINESS au 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>#nBusiness #GestionPME #Digitalisation #Commerce #Pressing #Éducation #NigerCertify #PME</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Post / Reels</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>NBUSINESS</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
+      <c r="N18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="90" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>3</v>
       </c>
@@ -1556,37 +1759,49 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Session PECB 10 oct. 2026 — inscriptions ouvertes</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>ISO 27001 · ISO 27701 · en ligne · 12 mois · 2 retakes · 350 000 FCFA
-WhatsApp 94 10 70 74 — JE M’INSCRIS</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Statut / CTA session</t>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Session PECB — inscriptions ouvertes (10 oct. 2026)</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Les inscriptions sont ouvertes pour la session PECB NigerCertify.
+📅 Démarrage : 10 octobre 2026
+💻 100 % en ligne
+📘 ISO/IEC 27001 · ISO/IEC 27701
+⏱ Accès plateforme 12 mois
+🔁 2 retakes examens inclus
+💰 Tarif : 350 000 FCFA
+Niger &amp; Sénégal — certification internationale, accompagnement local.
+👉 WhatsApp 94 10 70 74 — écrivez JE M’INSCRIS</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>#PECB #ISO27001 #ISO27701 #Cybersécurité #Certification #NigerCertify #Niger #Sénégal #FormationEnLigne</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>Post CTA session</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
+      <c r="N19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>4</v>
       </c>
@@ -1610,36 +1825,47 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Pourquoi ISO 27001 ?</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Le langage commun de la sécurité de l’information. Session PECB NigerCertify dès le 10/10/2026.</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Post carrousel / texte</t>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Pourquoi se certifier ISO 27001 ?</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>ISO 27001, c’est le langage commun de la sécurité de l’information.
+Avec NigerCertify, vous préparez votre certification PECB :
+• Session en ligne dès le 10 octobre 2026
+• Accès 12 mois + 2 retakes
+• Tarif : 350 000 FCFA
+Idéal pour RSSI, IT, consultants et équipes conformité.
+📩 Demandez le programme au 94 10 70 74 (mot-clé PROGRAMME)</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>#ISO27001 #PECB #SécuritéDeLInformation #SMSI #FormationIT #NigerCertify #AfriqueDeLOuest</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>Post texte / carrousel</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>PROGRAMME</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
+      <c r="N20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="90" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>4</v>
       </c>
@@ -1653,46 +1879,56 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Parcours LPI : LE → LPIC-1 → LPIC-2 → LPIC-3</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Format mixte. LE 150 000 FCFA · LPIC 200 000 FCFA / niveau.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Parcours LPI : de Linux Essentials à LPIC-3</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Admin Linux : un chemin clair avec NigerCertify.
+🐧 LPI LE (Linux Essentials) — 150 000 FCFA
+🐧 LPIC-1 · LPIC-2 · LPIC-3 — 200 000 FCFA / niveau
+📍 Format mixte (présentiel + en ligne)
+Progression : LE → LPIC-1 → LPIC-2 → LPIC-3
+Répondez LPI au 94 10 70 74 + votre niveau</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>#LPI #LPIC #Linux #LinuxEssentials #SysAdmin #NigerCertify #FormationLinux #OpenSource</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Post image + texte</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
+      <c r="N21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>4</v>
       </c>
@@ -1716,36 +1952,47 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Ce qui est inclus pour 350 000 FCFA</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Formation PECB + accès 12 mois + examen + 2 retakes + suivi NigerCertify.</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>350 000 FCFA : ce qui est vraiment inclus</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Pour 350 000 FCFA, la session PECB du 10/10/2026 inclut :
+✅ Formation PECB (ISO 27001 / 27701)
+✅ Accès en ligne 12 mois
+✅ Passage d’examen + 2 retakes
+✅ Accompagnement NigerCertify
+Pas de surprise. Un parcours clair pour réussir.
+WhatsApp 94 10 70 74 — répondez PECB</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>#PECB #Formation #ISO27001 #ISO27701 #CertificationPro #NigerCertify #InvestissementFormation</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Post texte + CTA</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>PECB</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
+      <c r="N22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="90" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>4</v>
       </c>
@@ -1759,50 +2006,65 @@
           <t>Jeu</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Linux Essentials — premier pas</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>TITRE : Linux Essentials — premier pas
-HOOK (0–5s) : Linux Essentials — premier pas
-CORPS : LPI LE · 150 000 FCFA · mixte. Idéal débutants &amp; reconversion.
-CTA fin : Écrivez LPI LE au 94 10 70 74
-DESCRIPTION : NigerCertify · Niger &amp; Sénégal · https://wa.me/22794107074?text=LPI%20LE</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Linux Essentials — le bon premier pas</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>TITRE VIDÉO : Linux Essentials — le bon premier pas
+HOOK (0–5 s) : Linux Essentials — le bon premier pas
+SCRIPT / CONTENU :
+Vous débutez sous Linux ou vous vous reconvertissez en IT ?
+LPI Linux Essentials (LPI LE) chez NigerCertify :
+• Bases système &amp; ligne de commande
+• Culture open source
+• Tarif : 150 000 FCFA
+• Format mixte
+Message LPI LE au 94 10 70 74
+CTA ÉCRAN DE FIN : Écrivez LPI LE au 94 10 70 74
+DESCRIPTION YOUTUBE :
+Vous débutez sous Linux ou vous vous reconvertissez en IT ?
+WhatsApp : https://wa.me/22794107074?text=LPI%20LE
+NigerCertify · Niger &amp; Sénégal</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>#LinuxEssentials #LPILE #Linux #ReconversionIT #Formation #NigerCertify #LPIC</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Vidéo 5–8 min</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>LPI LE</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
+      <c r="N23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="90" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>4</v>
       </c>
@@ -1816,46 +2078,57 @@
           <t>Ven</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>CouturePro</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>CouturePro — ateliers de couture</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Commandes, tissus, clients, délais — un seul outil.</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>CouturePro — le logiciel des ateliers de couture</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Les ateliers perdent du temps sans suivi clair.
+CouturePro vous aide à gérer :
+• Commandes clients
+• Stocks tissus &amp; fournitures
+• Délais de livraison
+Un outil simple pour les couturiers et stylistes.
+Démo : écrivez COUTUREPRO au 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>#CouturePro #AtelierCouture #Mode #Artisanat #Digitalisation #NigerCertify #GestionAtelier</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Post / Reels</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>COUTUREPRO</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
+      <c r="N24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>4</v>
       </c>
@@ -1879,36 +2152,45 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>ISO 27701 — privacy</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Protéger les données personnelles : extension naturelle du SMSI. Places session 10 oct.</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Statut / CTA session</t>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>ISO 27701 : la privacy au cœur du SMSI</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Protéger les données personnelles n’est plus optionnel.
+ISO/IEC 27701 complète ISO 27001 pour structurer la privacy.
+Session PECB NigerCertify — démarrage 10 octobre 2026
+En ligne · 12 mois · 2 retakes · 350 000 FCFA
+Places limitées → 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>#ISO27701 #Privacy #ProtectionDesDonnées #RGPD #PECB #NigerCertify #Conformité</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>Post CTA session</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>PROGRAMME</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
+      <c r="N25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="90" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>5</v>
       </c>
@@ -1932,36 +2214,46 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Niger &amp; Sénégal — même session en ligne</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Certification internationale, accompagnement local. 94 10 70 74</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Post carrousel / texte</t>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Niamey ↔ Dakar : une même session en ligne</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Que vous soyez au Niger ou au Sénégal, la session PECB est la même :
+• Exigence internationale
+• Accompagnement local NigerCertify
+• Démarrage 10 octobre 2026
+• 350 000 FCFA · 2 retakes
+Inscrivez-vous : WhatsApp 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>#Niger #Sénégal #PECB #FormationEnLigne #ISO27001 #NigerCertify #Certification</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>Post texte / carrousel</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
+      <c r="N26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>5</v>
       </c>
@@ -1975,46 +2267,57 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>LPIC-1 / 2 / 3 — montez en niveau</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Admin → Engineer → Enterprise. 200 000 FCFA / niveau · format mixte.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>LPIC-1, LPIC-2, LPIC-3 : montez en niveau</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Déjà à l’aise sous Linux ? Passez au niveau supérieur.
+• LPIC-1 — Administrateur
+• LPIC-2 — Engineer
+• LPIC-3 — Enterprise
+Tarif : 200 000 FCFA / niveau · Format mixte
+NigerCertify — Niger &amp; Sénégal
+WhatsApp 94 10 70 74 — mot-clé LPI</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>#LPIC1 #LPIC2 #LPIC3 #LinuxAdmin #DevOps #NigerCertify #CertificationLinux</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Post image + texte</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
+      <c r="N27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>5</v>
       </c>
@@ -2038,37 +2341,49 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Session PECB 10 oct. 2026 — inscriptions ouvertes</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>ISO 27001 · ISO 27701 · en ligne · 12 mois · 2 retakes · 350 000 FCFA
-WhatsApp 94 10 70 74 — JE M’INSCRIS</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Session PECB — inscriptions ouvertes (10 oct. 2026)</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Les inscriptions sont ouvertes pour la session PECB NigerCertify.
+📅 Démarrage : 10 octobre 2026
+💻 100 % en ligne
+📘 ISO/IEC 27001 · ISO/IEC 27701
+⏱ Accès plateforme 12 mois
+🔁 2 retakes examens inclus
+💰 Tarif : 350 000 FCFA
+Niger &amp; Sénégal — certification internationale, accompagnement local.
+👉 WhatsApp 94 10 70 74 — écrivez JE M’INSCRIS</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>#PECB #ISO27001 #ISO27701 #Cybersécurité #Certification #NigerCertify #Niger #Sénégal #FormationEnLigne</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Post texte + CTA</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
+      <c r="N28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>5</v>
       </c>
@@ -2092,40 +2407,55 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Pourquoi ISO 27001 ?</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>TITRE : Pourquoi ISO 27001 ?
-HOOK (0–5s) : Pourquoi ISO 27001 ?
-CORPS : Le langage commun de la sécurité de l’information. Session PECB NigerCertify dès le 10/10/2026.
-CTA fin : Écrivez PROGRAMME au 94 10 70 74
-DESCRIPTION : NigerCertify · Niger &amp; Sénégal · https://wa.me/22794107074?text=PROGRAMME</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Pourquoi se certifier ISO 27001 ?</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>TITRE VIDÉO : Pourquoi se certifier ISO 27001 ?
+HOOK (0–5 s) : Pourquoi se certifier ISO 27001 ?
+SCRIPT / CONTENU :
+ISO 27001, c’est le langage commun de la sécurité de l’information.
+Avec NigerCertify, vous préparez votre certification PECB :
+• Session en ligne dès le 10 octobre 2026
+• Accès 12 mois + 2 retakes
+• Tarif : 350 000 FCFA
+Idéal pour RSSI, IT, consultants et équipes conformité.
+📩 Demandez le programme au 94 10 70 74 (mot-clé PROGRAMME)
+CTA ÉCRAN DE FIN : Écrivez PROGRAMME au 94 10 70 74
+DESCRIPTION YOUTUBE :
+ISO 27001, c’est le langage commun de la sécurité de l’information.
+WhatsApp : https://wa.me/22794107074?text=PROGRAMME
+NigerCertify · Niger &amp; Sénégal</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>#ISO27001 #PECB #SécuritéDeLInformation #SMSI #FormationIT #NigerCertify #AfriqueDeLOuest</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>Vidéo 5–8 min</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>PROGRAMME</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
+      <c r="N29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="90" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>5</v>
       </c>
@@ -2139,46 +2469,54 @@
           <t>Ven</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>nBusiness</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Démo nBusiness 10 min</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Réservez une démo WhatsApp. 94 10 70 74</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Démo nBusiness en 10 minutes</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Envie de voir nBusiness en action ?
+On vous montre en 10 minutes sur WhatsApp comment suivre stock, clients et ventes.
+Idéal commerce, école, pressing et business.
+Réservez : 94 10 70 74 — mot-clé NBUSINESS</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>#nBusiness #DémoLogiciel #PME #GestionCommerciale #Niger #Sénégal #NigerCertify</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Post / Reels</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>NBUSINESS</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
+      <c r="N30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="90" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>5</v>
       </c>
@@ -2202,36 +2540,47 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Ce qui est inclus pour 350 000 FCFA</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Formation PECB + accès 12 mois + examen + 2 retakes + suivi NigerCertify.</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Statut / CTA session</t>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>350 000 FCFA : ce qui est vraiment inclus</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Pour 350 000 FCFA, la session PECB du 10/10/2026 inclut :
+✅ Formation PECB (ISO 27001 / 27701)
+✅ Accès en ligne 12 mois
+✅ Passage d’examen + 2 retakes
+✅ Accompagnement NigerCertify
+Pas de surprise. Un parcours clair pour réussir.
+WhatsApp 94 10 70 74 — répondez PECB</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>#PECB #Formation #ISO27001 #ISO27701 #CertificationPro #NigerCertify #InvestissementFormation</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
+          <t>Post CTA session</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>PECB</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
+      <c r="N31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="90" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>6</v>
       </c>
@@ -2255,36 +2604,45 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>ISO 27701 — privacy</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Protéger les données personnelles : extension naturelle du SMSI. Places session 10 oct.</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Post carrousel / texte</t>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>ISO 27701 : la privacy au cœur du SMSI</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Protéger les données personnelles n’est plus optionnel.
+ISO/IEC 27701 complète ISO 27001 pour structurer la privacy.
+Session PECB NigerCertify — démarrage 10 octobre 2026
+En ligne · 12 mois · 2 retakes · 350 000 FCFA
+Places limitées → 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>#ISO27701 #Privacy #ProtectionDesDonnées #RGPD #PECB #NigerCertify #Conformité</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>Post texte / carrousel</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>PROGRAMME</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
+      <c r="N32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="90" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>6</v>
       </c>
@@ -2298,46 +2656,56 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Tip Linux (60 sec)</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Une commande utile + lien vers le parcours LPI NigerCertify.</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Tip Linux : une commande, un métier</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Maîtriser Linux, c’est maîtriser le terrain IT.
+Chaque semaine, NigerCertify vous prépare aux certifications LPI :
+LE (150 000 FCFA) · LPIC-1/2/3 (200 000 FCFA) · format mixte.
+Aujourd’hui : prenez 10 minutes pour réviser une commande.
+Demain : visez la certif.
+Écrivez LPI au 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>#LinuxTip #LPI #SysAdmin #Terminal #OpenSource #NigerCertify #FormationIT</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Post image + texte</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
+      <c r="N33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="90" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>6</v>
       </c>
@@ -2361,36 +2729,46 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Niger &amp; Sénégal — même session en ligne</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Certification internationale, accompagnement local. 94 10 70 74</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Niamey ↔ Dakar : une même session en ligne</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Que vous soyez au Niger ou au Sénégal, la session PECB est la même :
+• Exigence internationale
+• Accompagnement local NigerCertify
+• Démarrage 10 octobre 2026
+• 350 000 FCFA · 2 retakes
+Inscrivez-vous : WhatsApp 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>#Niger #Sénégal #PECB #FormationEnLigne #ISO27001 #NigerCertify #Certification</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Post texte + CTA</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
+      <c r="N34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35" ht="90" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>6</v>
       </c>
@@ -2404,50 +2782,64 @@
           <t>Jeu</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Parcours LPI : LE → LPIC-1 → LPIC-2 → LPIC-3</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>TITRE : Parcours LPI : LE → LPIC-1 → LPIC-2 → LPIC-3
-HOOK (0–5s) : Parcours LPI : LE → LPIC-1 → LPIC-2 → LPIC-3
-CORPS : Format mixte. LE 150 000 FCFA · LPIC 200 000 FCFA / niveau.
-CTA fin : Écrivez LPI au 94 10 70 74
-DESCRIPTION : NigerCertify · Niger &amp; Sénégal · https://wa.me/22794107074?text=LPI</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Parcours LPI : de Linux Essentials à LPIC-3</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>TITRE VIDÉO : Parcours LPI : de Linux Essentials à LPIC-3
+HOOK (0–5 s) : Parcours LPI : de Linux Essentials à LPIC-3
+SCRIPT / CONTENU :
+Admin Linux : un chemin clair avec NigerCertify.
+🐧 LPI LE (Linux Essentials) — 150 000 FCFA
+🐧 LPIC-1 · LPIC-2 · LPIC-3 — 200 000 FCFA / niveau
+📍 Format mixte (présentiel + en ligne)
+Progression : LE → LPIC-1 → LPIC-2 → LPIC-3
+Répondez LPI au 94 10 70 74 + votre niveau
+CTA ÉCRAN DE FIN : Écrivez LPI au 94 10 70 74
+DESCRIPTION YOUTUBE :
+Admin Linux : un chemin clair avec NigerCertify.
+WhatsApp : https://wa.me/22794107074?text=LPI
+NigerCertify · Niger &amp; Sénégal</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>#LPI #LPIC #Linux #LinuxEssentials #SysAdmin #NigerCertify #FormationLinux #OpenSource</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>YouTube Short (45–60s)</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
+      <c r="N35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="90" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>6</v>
       </c>
@@ -2461,46 +2853,57 @@
           <t>Ven</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>nBusiness</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>nBusiness — gestion multi-secteur</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Commerce, école, pressing, business : stock, clients, ventes.</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>nBusiness — la gestion multi-secteur</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Commerce, école, pressing, business…
+nBusiness centralise :
+• Stocks
+• Clients
+• Ventes
+Sans usine à gaz. Pensé pour les PME du Niger et du Sénégal.
+Démo 10 min : écrivez NBUSINESS au 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>#nBusiness #GestionPME #Digitalisation #Commerce #Pressing #Éducation #NigerCertify #PME</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Post / Reels</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>NBUSINESS</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
+      <c r="N36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="90" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>6</v>
       </c>
@@ -2524,37 +2927,49 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Session PECB 10 oct. 2026 — inscriptions ouvertes</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>ISO 27001 · ISO 27701 · en ligne · 12 mois · 2 retakes · 350 000 FCFA
-WhatsApp 94 10 70 74 — JE M’INSCRIS</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Statut / CTA session</t>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Session PECB — inscriptions ouvertes (10 oct. 2026)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Les inscriptions sont ouvertes pour la session PECB NigerCertify.
+📅 Démarrage : 10 octobre 2026
+💻 100 % en ligne
+📘 ISO/IEC 27001 · ISO/IEC 27701
+⏱ Accès plateforme 12 mois
+🔁 2 retakes examens inclus
+💰 Tarif : 350 000 FCFA
+Niger &amp; Sénégal — certification internationale, accompagnement local.
+👉 WhatsApp 94 10 70 74 — écrivez JE M’INSCRIS</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>#PECB #ISO27001 #ISO27701 #Cybersécurité #Certification #NigerCertify #Niger #Sénégal #FormationEnLigne</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
+          <t>Post CTA session</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
+      <c r="N37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="90" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>7</v>
       </c>
@@ -2578,36 +2993,47 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Pourquoi ISO 27001 ?</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Le langage commun de la sécurité de l’information. Session PECB NigerCertify dès le 10/10/2026.</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Post carrousel / texte</t>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Pourquoi se certifier ISO 27001 ?</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>ISO 27001, c’est le langage commun de la sécurité de l’information.
+Avec NigerCertify, vous préparez votre certification PECB :
+• Session en ligne dès le 10 octobre 2026
+• Accès 12 mois + 2 retakes
+• Tarif : 350 000 FCFA
+Idéal pour RSSI, IT, consultants et équipes conformité.
+📩 Demandez le programme au 94 10 70 74 (mot-clé PROGRAMME)</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>#ISO27001 #PECB #SécuritéDeLInformation #SMSI #FormationIT #NigerCertify #AfriqueDeLOuest</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
+          <t>Post texte / carrousel</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>PROGRAMME</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
+      <c r="N38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="90" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>7</v>
       </c>
@@ -2621,46 +3047,57 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Linux Essentials — premier pas</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>LPI LE · 150 000 FCFA · mixte. Idéal débutants &amp; reconversion.</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Linux Essentials — le bon premier pas</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Vous débutez sous Linux ou vous vous reconvertissez en IT ?
+LPI Linux Essentials (LPI LE) chez NigerCertify :
+• Bases système &amp; ligne de commande
+• Culture open source
+• Tarif : 150 000 FCFA
+• Format mixte
+Message LPI LE au 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>#LinuxEssentials #LPILE #Linux #ReconversionIT #Formation #NigerCertify #LPIC</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>Post image + texte</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>LPI LE</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
+      <c r="N39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="90" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>7</v>
       </c>
@@ -2684,36 +3121,47 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Ce qui est inclus pour 350 000 FCFA</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Formation PECB + accès 12 mois + examen + 2 retakes + suivi NigerCertify.</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>350 000 FCFA : ce qui est vraiment inclus</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Pour 350 000 FCFA, la session PECB du 10/10/2026 inclut :
+✅ Formation PECB (ISO 27001 / 27701)
+✅ Accès en ligne 12 mois
+✅ Passage d’examen + 2 retakes
+✅ Accompagnement NigerCertify
+Pas de surprise. Un parcours clair pour réussir.
+WhatsApp 94 10 70 74 — répondez PECB</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>#PECB #Formation #ISO27001 #ISO27701 #CertificationPro #NigerCertify #InvestissementFormation</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>Post texte + CTA</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>PECB</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
+      <c r="N40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="90" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>7</v>
       </c>
@@ -2737,40 +3185,53 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>ISO 27701 — privacy</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>TITRE : ISO 27701 — privacy
-HOOK (0–5s) : ISO 27701 — privacy
-CORPS : Protéger les données personnelles : extension naturelle du SMSI. Places session 10 oct.
-CTA fin : Écrivez PROGRAMME au 94 10 70 74
-DESCRIPTION : NigerCertify · Niger &amp; Sénégal · https://wa.me/22794107074?text=PROGRAMME</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>ISO 27701 : la privacy au cœur du SMSI</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>TITRE VIDÉO : ISO 27701 : la privacy au cœur du SMSI
+HOOK (0–5 s) : ISO 27701 : la privacy au cœur du SMSI
+SCRIPT / CONTENU :
+Protéger les données personnelles n’est plus optionnel.
+ISO/IEC 27701 complète ISO 27001 pour structurer la privacy.
+Session PECB NigerCertify — démarrage 10 octobre 2026
+En ligne · 12 mois · 2 retakes · 350 000 FCFA
+Places limitées → 94 10 70 74
+CTA ÉCRAN DE FIN : Écrivez PROGRAMME au 94 10 70 74
+DESCRIPTION YOUTUBE :
+Protéger les données personnelles n’est plus optionnel.
+WhatsApp : https://wa.me/22794107074?text=PROGRAMME
+NigerCertify · Niger &amp; Sénégal</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>#ISO27701 #Privacy #ProtectionDesDonnées #RGPD #PECB #NigerCertify #Conformité</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>Vidéo 5–8 min</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>PROGRAMME</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
+      <c r="N41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="90" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>7</v>
       </c>
@@ -2784,46 +3245,54 @@
           <t>Ven</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>nBusiness</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Démo nBusiness 10 min</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Réservez une démo WhatsApp. 94 10 70 74</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Démo nBusiness en 10 minutes</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Envie de voir nBusiness en action ?
+On vous montre en 10 minutes sur WhatsApp comment suivre stock, clients et ventes.
+Idéal commerce, école, pressing et business.
+Réservez : 94 10 70 74 — mot-clé NBUSINESS</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>#nBusiness #DémoLogiciel #PME #GestionCommerciale #Niger #Sénégal #NigerCertify</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>Post / Reels</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>NBUSINESS</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
+      <c r="N42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="90" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>7</v>
       </c>
@@ -2847,36 +3316,46 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Niger &amp; Sénégal — même session en ligne</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Certification internationale, accompagnement local. 94 10 70 74</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Statut / CTA session</t>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Niamey ↔ Dakar : une même session en ligne</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Que vous soyez au Niger ou au Sénégal, la session PECB est la même :
+• Exigence internationale
+• Accompagnement local NigerCertify
+• Démarrage 10 octobre 2026
+• 350 000 FCFA · 2 retakes
+Inscrivez-vous : WhatsApp 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>#Niger #Sénégal #PECB #FormationEnLigne #ISO27001 #NigerCertify #Certification</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
+          <t>Post CTA session</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
+      <c r="N43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="90" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>8</v>
       </c>
@@ -2900,37 +3379,49 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Session PECB 10 oct. 2026 — inscriptions ouvertes</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>ISO 27001 · ISO 27701 · en ligne · 12 mois · 2 retakes · 350 000 FCFA
-WhatsApp 94 10 70 74 — JE M’INSCRIS</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Post carrousel / texte</t>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Session PECB — inscriptions ouvertes (10 oct. 2026)</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Les inscriptions sont ouvertes pour la session PECB NigerCertify.
+📅 Démarrage : 10 octobre 2026
+💻 100 % en ligne
+📘 ISO/IEC 27001 · ISO/IEC 27701
+⏱ Accès plateforme 12 mois
+🔁 2 retakes examens inclus
+💰 Tarif : 350 000 FCFA
+Niger &amp; Sénégal — certification internationale, accompagnement local.
+👉 WhatsApp 94 10 70 74 — écrivez JE M’INSCRIS</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>#PECB #ISO27001 #ISO27701 #Cybersécurité #Certification #NigerCertify #Niger #Sénégal #FormationEnLigne</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
+          <t>Post texte / carrousel</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
+      <c r="N44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="90" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>8</v>
       </c>
@@ -2944,46 +3435,57 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>LPIC-1 / 2 / 3 — montez en niveau</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Admin → Engineer → Enterprise. 200 000 FCFA / niveau · format mixte.</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>LPIC-1, LPIC-2, LPIC-3 : montez en niveau</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Déjà à l’aise sous Linux ? Passez au niveau supérieur.
+• LPIC-1 — Administrateur
+• LPIC-2 — Engineer
+• LPIC-3 — Enterprise
+Tarif : 200 000 FCFA / niveau · Format mixte
+NigerCertify — Niger &amp; Sénégal
+WhatsApp 94 10 70 74 — mot-clé LPI</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>#LPIC1 #LPIC2 #LPIC3 #LinuxAdmin #DevOps #NigerCertify #CertificationLinux</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>Post image + texte</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
+      <c r="N45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="90" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>8</v>
       </c>
@@ -3007,36 +3509,47 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Pourquoi ISO 27001 ?</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Le langage commun de la sécurité de l’information. Session PECB NigerCertify dès le 10/10/2026.</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Pourquoi se certifier ISO 27001 ?</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>ISO 27001, c’est le langage commun de la sécurité de l’information.
+Avec NigerCertify, vous préparez votre certification PECB :
+• Session en ligne dès le 10 octobre 2026
+• Accès 12 mois + 2 retakes
+• Tarif : 350 000 FCFA
+Idéal pour RSSI, IT, consultants et équipes conformité.
+📩 Demandez le programme au 94 10 70 74 (mot-clé PROGRAMME)</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>#ISO27001 #PECB #SécuritéDeLInformation #SMSI #FormationIT #NigerCertify #AfriqueDeLOuest</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>Post texte + CTA</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>PROGRAMME</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
+      <c r="N46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="90" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>8</v>
       </c>
@@ -3050,50 +3563,64 @@
           <t>Jeu</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Tip Linux (60 sec)</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>TITRE : Tip Linux (60 sec)
-HOOK (0–5s) : Tip Linux (60 sec)
-CORPS : Une commande utile + lien vers le parcours LPI NigerCertify.
-CTA fin : Écrivez LPI au 94 10 70 74
-DESCRIPTION : NigerCertify · Niger &amp; Sénégal · https://wa.me/22794107074?text=LPI</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Tip Linux : une commande, un métier</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>TITRE VIDÉO : Tip Linux : une commande, un métier
+HOOK (0–5 s) : Tip Linux : une commande, un métier
+SCRIPT / CONTENU :
+Maîtriser Linux, c’est maîtriser le terrain IT.
+Chaque semaine, NigerCertify vous prépare aux certifications LPI :
+LE (150 000 FCFA) · LPIC-1/2/3 (200 000 FCFA) · format mixte.
+Aujourd’hui : prenez 10 minutes pour réviser une commande.
+Demain : visez la certif.
+Écrivez LPI au 94 10 70 74
+CTA ÉCRAN DE FIN : Écrivez LPI au 94 10 70 74
+DESCRIPTION YOUTUBE :
+Maîtriser Linux, c’est maîtriser le terrain IT.
+WhatsApp : https://wa.me/22794107074?text=LPI
+NigerCertify · Niger &amp; Sénégal</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>#LinuxTip #LPI #SysAdmin #Terminal #OpenSource #NigerCertify #FormationIT</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>Vidéo 5–8 min</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
+      <c r="N47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="90" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>8</v>
       </c>
@@ -3107,46 +3634,57 @@
           <t>Ven</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E48" s="10" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>CouturePro</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>CouturePro — ateliers de couture</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Commandes, tissus, clients, délais — un seul outil.</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>CouturePro — le logiciel des ateliers de couture</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>Les ateliers perdent du temps sans suivi clair.
+CouturePro vous aide à gérer :
+• Commandes clients
+• Stocks tissus &amp; fournitures
+• Délais de livraison
+Un outil simple pour les couturiers et stylistes.
+Démo : écrivez COUTUREPRO au 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>#CouturePro #AtelierCouture #Mode #Artisanat #Digitalisation #NigerCertify #GestionAtelier</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>Post / Reels</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>COUTUREPRO</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
+      <c r="N48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="90" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>8</v>
       </c>
@@ -3170,36 +3708,47 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Ce qui est inclus pour 350 000 FCFA</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Formation PECB + accès 12 mois + examen + 2 retakes + suivi NigerCertify.</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Statut / CTA session</t>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>350 000 FCFA : ce qui est vraiment inclus</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Pour 350 000 FCFA, la session PECB du 10/10/2026 inclut :
+✅ Formation PECB (ISO 27001 / 27701)
+✅ Accès en ligne 12 mois
+✅ Passage d’examen + 2 retakes
+✅ Accompagnement NigerCertify
+Pas de surprise. Un parcours clair pour réussir.
+WhatsApp 94 10 70 74 — répondez PECB</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>#PECB #Formation #ISO27001 #ISO27701 #CertificationPro #NigerCertify #InvestissementFormation</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
+          <t>Post CTA session</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>PECB</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
+      <c r="N49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50" ht="90" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>9</v>
       </c>
@@ -3223,36 +3772,45 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>ISO 27701 — privacy</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Protéger les données personnelles : extension naturelle du SMSI. Places session 10 oct.</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Post carrousel / texte</t>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>ISO 27701 : la privacy au cœur du SMSI</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>Protéger les données personnelles n’est plus optionnel.
+ISO/IEC 27701 complète ISO 27001 pour structurer la privacy.
+Session PECB NigerCertify — démarrage 10 octobre 2026
+En ligne · 12 mois · 2 retakes · 350 000 FCFA
+Places limitées → 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>#ISO27701 #Privacy #ProtectionDesDonnées #RGPD #PECB #NigerCertify #Conformité</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
+          <t>Post texte / carrousel</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>PROGRAMME</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
+      <c r="N50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="90" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>9</v>
       </c>
@@ -3266,46 +3824,56 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Parcours LPI : LE → LPIC-1 → LPIC-2 → LPIC-3</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Format mixte. LE 150 000 FCFA · LPIC 200 000 FCFA / niveau.</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Parcours LPI : de Linux Essentials à LPIC-3</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Admin Linux : un chemin clair avec NigerCertify.
+🐧 LPI LE (Linux Essentials) — 150 000 FCFA
+🐧 LPIC-1 · LPIC-2 · LPIC-3 — 200 000 FCFA / niveau
+📍 Format mixte (présentiel + en ligne)
+Progression : LE → LPIC-1 → LPIC-2 → LPIC-3
+Répondez LPI au 94 10 70 74 + votre niveau</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>#LPI #LPIC #Linux #LinuxEssentials #SysAdmin #NigerCertify #FormationLinux #OpenSource</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>Post image + texte</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
+      <c r="N51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="90" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>9</v>
       </c>
@@ -3329,36 +3897,46 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Niger &amp; Sénégal — même session en ligne</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Certification internationale, accompagnement local. 94 10 70 74</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Niamey ↔ Dakar : une même session en ligne</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Que vous soyez au Niger ou au Sénégal, la session PECB est la même :
+• Exigence internationale
+• Accompagnement local NigerCertify
+• Démarrage 10 octobre 2026
+• 350 000 FCFA · 2 retakes
+Inscrivez-vous : WhatsApp 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>#Niger #Sénégal #PECB #FormationEnLigne #ISO27001 #NigerCertify #Certification</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>Post texte + CTA</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
+      <c r="N52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="90" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>9</v>
       </c>
@@ -3382,41 +3960,57 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Session PECB 10 oct. 2026 — inscriptions ouvertes</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>TITRE : Session PECB 10 oct. 2026 — inscriptions ouvertes
-HOOK (0–5s) : Session PECB 10 oct. 2026 — inscriptions ouvertes
-CORPS : ISO 27001 · ISO 27701 · en ligne · 12 mois · 2 retakes · 350 000 FCFA
-WhatsApp 94 10 70 74 — JE M’INSCRIS
-CTA fin : Écrivez JE M’INSCRIS au 94 10 70 74
-DESCRIPTION : NigerCertify · Niger &amp; Sénégal · https://wa.me/22794107074?text=JE%20M’INSCRIS</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Session PECB — inscriptions ouvertes (10 oct. 2026)</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>TITRE VIDÉO : Session PECB — inscriptions ouvertes (10 oct. 2026)
+HOOK (0–5 s) : Session PECB — inscriptions ouvertes (10 oct. 2026)
+SCRIPT / CONTENU :
+Les inscriptions sont ouvertes pour la session PECB NigerCertify.
+📅 Démarrage : 10 octobre 2026
+💻 100 % en ligne
+📘 ISO/IEC 27001 · ISO/IEC 27701
+⏱ Accès plateforme 12 mois
+🔁 2 retakes examens inclus
+💰 Tarif : 350 000 FCFA
+Niger &amp; Sénégal — certification internationale, accompagnement local.
+👉 WhatsApp 94 10 70 74 — écrivez JE M’INSCRIS
+CTA ÉCRAN DE FIN : Écrivez JE M’INSCRIS au 94 10 70 74
+DESCRIPTION YOUTUBE :
+Les inscriptions sont ouvertes pour la session PECB NigerCertify.
+WhatsApp : https://wa.me/22794107074?text=JE%20M’INSCRIS
+NigerCertify · Niger &amp; Sénégal</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>#PECB #ISO27001 #ISO27701 #Cybersécurité #Certification #NigerCertify #Niger #Sénégal #FormationEnLigne</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>YouTube Short (45–60s)</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
+      <c r="N53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="90" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>9</v>
       </c>
@@ -3430,46 +4024,57 @@
           <t>Ven</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
         <is>
           <t>nBusiness</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>nBusiness — gestion multi-secteur</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Commerce, école, pressing, business : stock, clients, ventes.</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>nBusiness — la gestion multi-secteur</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Commerce, école, pressing, business…
+nBusiness centralise :
+• Stocks
+• Clients
+• Ventes
+Sans usine à gaz. Pensé pour les PME du Niger et du Sénégal.
+Démo 10 min : écrivez NBUSINESS au 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>#nBusiness #GestionPME #Digitalisation #Commerce #Pressing #Éducation #NigerCertify #PME</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>Post / Reels</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>NBUSINESS</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
+      <c r="N54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55" ht="90" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>9</v>
       </c>
@@ -3493,36 +4098,47 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Pourquoi ISO 27001 ?</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Le langage commun de la sécurité de l’information. Session PECB NigerCertify dès le 10/10/2026.</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Statut / CTA session</t>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Pourquoi se certifier ISO 27001 ?</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>ISO 27001, c’est le langage commun de la sécurité de l’information.
+Avec NigerCertify, vous préparez votre certification PECB :
+• Session en ligne dès le 10 octobre 2026
+• Accès 12 mois + 2 retakes
+• Tarif : 350 000 FCFA
+Idéal pour RSSI, IT, consultants et équipes conformité.
+📩 Demandez le programme au 94 10 70 74 (mot-clé PROGRAMME)</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>#ISO27001 #PECB #SécuritéDeLInformation #SMSI #FormationIT #NigerCertify #AfriqueDeLOuest</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
+          <t>Post CTA session</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>PROGRAMME</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
+      <c r="N55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56" ht="90" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>10</v>
       </c>
@@ -3546,36 +4162,47 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Ce qui est inclus pour 350 000 FCFA</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Formation PECB + accès 12 mois + examen + 2 retakes + suivi NigerCertify.</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Post carrousel / texte</t>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>350 000 FCFA : ce qui est vraiment inclus</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Pour 350 000 FCFA, la session PECB du 10/10/2026 inclut :
+✅ Formation PECB (ISO 27001 / 27701)
+✅ Accès en ligne 12 mois
+✅ Passage d’examen + 2 retakes
+✅ Accompagnement NigerCertify
+Pas de surprise. Un parcours clair pour réussir.
+WhatsApp 94 10 70 74 — répondez PECB</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>#PECB #Formation #ISO27001 #ISO27701 #CertificationPro #NigerCertify #InvestissementFormation</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
+          <t>Post texte / carrousel</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>PECB</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
+      <c r="N56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="90" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>10</v>
       </c>
@@ -3589,46 +4216,57 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Linux Essentials — premier pas</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>LPI LE · 150 000 FCFA · mixte. Idéal débutants &amp; reconversion.</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Linux Essentials — le bon premier pas</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Vous débutez sous Linux ou vous vous reconvertissez en IT ?
+LPI Linux Essentials (LPI LE) chez NigerCertify :
+• Bases système &amp; ligne de commande
+• Culture open source
+• Tarif : 150 000 FCFA
+• Format mixte
+Message LPI LE au 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>#LinuxEssentials #LPILE #Linux #ReconversionIT #Formation #NigerCertify #LPIC</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>Post image + texte</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>LPI LE</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
+      <c r="N57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58" ht="90" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>10</v>
       </c>
@@ -3652,36 +4290,45 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>ISO 27701 — privacy</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Protéger les données personnelles : extension naturelle du SMSI. Places session 10 oct.</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>ISO 27701 : la privacy au cœur du SMSI</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Protéger les données personnelles n’est plus optionnel.
+ISO/IEC 27701 complète ISO 27001 pour structurer la privacy.
+Session PECB NigerCertify — démarrage 10 octobre 2026
+En ligne · 12 mois · 2 retakes · 350 000 FCFA
+Places limitées → 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>#ISO27701 #Privacy #ProtectionDesDonnées #RGPD #PECB #NigerCertify #Conformité</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
         <is>
           <t>Post texte + CTA</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>PROGRAMME</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
+      <c r="N58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="90" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>10</v>
       </c>
@@ -3695,50 +4342,65 @@
           <t>Jeu</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>LPIC-1 / 2 / 3 — montez en niveau</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>TITRE : LPIC-1 / 2 / 3 — montez en niveau
-HOOK (0–5s) : LPIC-1 / 2 / 3 — montez en niveau
-CORPS : Admin → Engineer → Enterprise. 200 000 FCFA / niveau · format mixte.
-CTA fin : Écrivez LPI au 94 10 70 74
-DESCRIPTION : NigerCertify · Niger &amp; Sénégal · https://wa.me/22794107074?text=LPI</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>LPIC-1, LPIC-2, LPIC-3 : montez en niveau</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>TITRE VIDÉO : LPIC-1, LPIC-2, LPIC-3 : montez en niveau
+HOOK (0–5 s) : LPIC-1, LPIC-2, LPIC-3 : montez en niveau
+SCRIPT / CONTENU :
+Déjà à l’aise sous Linux ? Passez au niveau supérieur.
+• LPIC-1 — Administrateur
+• LPIC-2 — Engineer
+• LPIC-3 — Enterprise
+Tarif : 200 000 FCFA / niveau · Format mixte
+NigerCertify — Niger &amp; Sénégal
+WhatsApp 94 10 70 74 — mot-clé LPI
+CTA ÉCRAN DE FIN : Écrivez LPI au 94 10 70 74
+DESCRIPTION YOUTUBE :
+Déjà à l’aise sous Linux ? Passez au niveau supérieur.
+WhatsApp : https://wa.me/22794107074?text=LPI
+NigerCertify · Niger &amp; Sénégal</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>#LPIC1 #LPIC2 #LPIC3 #LinuxAdmin #DevOps #NigerCertify #CertificationLinux</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t>Vidéo 5–8 min</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
+      <c r="N59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60" ht="90" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>10</v>
       </c>
@@ -3752,46 +4414,54 @@
           <t>Ven</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>nBusiness</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Démo nBusiness 10 min</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Réservez une démo WhatsApp. 94 10 70 74</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>Démo nBusiness en 10 minutes</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>Envie de voir nBusiness en action ?
+On vous montre en 10 minutes sur WhatsApp comment suivre stock, clients et ventes.
+Idéal commerce, école, pressing et business.
+Réservez : 94 10 70 74 — mot-clé NBUSINESS</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>#nBusiness #DémoLogiciel #PME #GestionCommerciale #Niger #Sénégal #NigerCertify</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
         <is>
           <t>Post / Reels</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>NBUSINESS</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
+      <c r="N60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="90" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>10</v>
       </c>
@@ -3815,36 +4485,46 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Niger &amp; Sénégal — même session en ligne</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Certification internationale, accompagnement local. 94 10 70 74</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Statut / CTA session</t>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Niamey ↔ Dakar : une même session en ligne</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Que vous soyez au Niger ou au Sénégal, la session PECB est la même :
+• Exigence internationale
+• Accompagnement local NigerCertify
+• Démarrage 10 octobre 2026
+• 350 000 FCFA · 2 retakes
+Inscrivez-vous : WhatsApp 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>#Niger #Sénégal #PECB #FormationEnLigne #ISO27001 #NigerCertify #Certification</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
+          <t>Post CTA session</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
+      <c r="N61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62" ht="90" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>11</v>
       </c>
@@ -3868,37 +4548,49 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>Session PECB 10 oct. 2026 — inscriptions ouvertes</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>ISO 27001 · ISO 27701 · en ligne · 12 mois · 2 retakes · 350 000 FCFA
-WhatsApp 94 10 70 74 — JE M’INSCRIS</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>Post carrousel / texte</t>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>Session PECB — inscriptions ouvertes (10 oct. 2026)</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>Les inscriptions sont ouvertes pour la session PECB NigerCertify.
+📅 Démarrage : 10 octobre 2026
+💻 100 % en ligne
+📘 ISO/IEC 27001 · ISO/IEC 27701
+⏱ Accès plateforme 12 mois
+🔁 2 retakes examens inclus
+💰 Tarif : 350 000 FCFA
+Niger &amp; Sénégal — certification internationale, accompagnement local.
+👉 WhatsApp 94 10 70 74 — écrivez JE M’INSCRIS</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>#PECB #ISO27001 #ISO27701 #Cybersécurité #Certification #NigerCertify #Niger #Sénégal #FormationEnLigne</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
+          <t>Post texte / carrousel</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
+      <c r="N62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" ht="90" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>11</v>
       </c>
@@ -3912,46 +4604,56 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>Tip Linux (60 sec)</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Une commande utile + lien vers le parcours LPI NigerCertify.</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Tip Linux : une commande, un métier</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Maîtriser Linux, c’est maîtriser le terrain IT.
+Chaque semaine, NigerCertify vous prépare aux certifications LPI :
+LE (150 000 FCFA) · LPIC-1/2/3 (200 000 FCFA) · format mixte.
+Aujourd’hui : prenez 10 minutes pour réviser une commande.
+Demain : visez la certif.
+Écrivez LPI au 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>#LinuxTip #LPI #SysAdmin #Terminal #OpenSource #NigerCertify #FormationIT</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t>Post image + texte</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
+      <c r="N63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="90" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>11</v>
       </c>
@@ -3975,36 +4677,47 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>Pourquoi ISO 27001 ?</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Le langage commun de la sécurité de l’information. Session PECB NigerCertify dès le 10/10/2026.</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>Pourquoi se certifier ISO 27001 ?</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>ISO 27001, c’est le langage commun de la sécurité de l’information.
+Avec NigerCertify, vous préparez votre certification PECB :
+• Session en ligne dès le 10 octobre 2026
+• Accès 12 mois + 2 retakes
+• Tarif : 350 000 FCFA
+Idéal pour RSSI, IT, consultants et équipes conformité.
+📩 Demandez le programme au 94 10 70 74 (mot-clé PROGRAMME)</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>#ISO27001 #PECB #SécuritéDeLInformation #SMSI #FormationIT #NigerCertify #AfriqueDeLOuest</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>Post texte + CTA</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>PROGRAMME</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
+      <c r="N64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65" ht="90" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>11</v>
       </c>
@@ -4028,40 +4741,55 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>Ce qui est inclus pour 350 000 FCFA</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>TITRE : Ce qui est inclus pour 350 000 FCFA
-HOOK (0–5s) : Ce qui est inclus pour 350 000 FCFA
-CORPS : Formation PECB + accès 12 mois + examen + 2 retakes + suivi NigerCertify.
-CTA fin : Écrivez PECB au 94 10 70 74
-DESCRIPTION : NigerCertify · Niger &amp; Sénégal · https://wa.me/22794107074?text=PECB</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>350 000 FCFA : ce qui est vraiment inclus</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>TITRE VIDÉO : 350 000 FCFA : ce qui est vraiment inclus
+HOOK (0–5 s) : 350 000 FCFA : ce qui est vraiment inclus
+SCRIPT / CONTENU :
+Pour 350 000 FCFA, la session PECB du 10/10/2026 inclut :
+✅ Formation PECB (ISO 27001 / 27701)
+✅ Accès en ligne 12 mois
+✅ Passage d’examen + 2 retakes
+✅ Accompagnement NigerCertify
+Pas de surprise. Un parcours clair pour réussir.
+WhatsApp 94 10 70 74 — répondez PECB
+CTA ÉCRAN DE FIN : Écrivez PECB au 94 10 70 74
+DESCRIPTION YOUTUBE :
+Pour 350 000 FCFA, la session PECB du 10/10/2026 inclut :
+WhatsApp : https://wa.me/22794107074?text=PECB
+NigerCertify · Niger &amp; Sénégal</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>#PECB #Formation #ISO27001 #ISO27701 #CertificationPro #NigerCertify #InvestissementFormation</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t>Vidéo 5–8 min</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="J65" s="2" t="inlineStr">
         <is>
           <t>PECB</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
+      <c r="N65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66" ht="90" customHeight="1">
       <c r="A66" s="2" t="n">
         <v>11</v>
       </c>
@@ -4075,46 +4803,57 @@
           <t>Ven</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D66" s="8" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
+      <c r="E66" s="9" t="inlineStr">
         <is>
           <t>nBusiness</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>nBusiness — gestion multi-secteur</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Commerce, école, pressing, business : stock, clients, ventes.</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>nBusiness — la gestion multi-secteur</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>Commerce, école, pressing, business…
+nBusiness centralise :
+• Stocks
+• Clients
+• Ventes
+Sans usine à gaz. Pensé pour les PME du Niger et du Sénégal.
+Démo 10 min : écrivez NBUSINESS au 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>#nBusiness #GestionPME #Digitalisation #Commerce #Pressing #Éducation #NigerCertify #PME</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>Post / Reels</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>NBUSINESS</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
+      <c r="N66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67" ht="90" customHeight="1">
       <c r="A67" s="2" t="n">
         <v>11</v>
       </c>
@@ -4138,36 +4877,45 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>ISO 27701 — privacy</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Protéger les données personnelles : extension naturelle du SMSI. Places session 10 oct.</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>Statut / CTA session</t>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>ISO 27701 : la privacy au cœur du SMSI</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Protéger les données personnelles n’est plus optionnel.
+ISO/IEC 27701 complète ISO 27001 pour structurer la privacy.
+Session PECB NigerCertify — démarrage 10 octobre 2026
+En ligne · 12 mois · 2 retakes · 350 000 FCFA
+Places limitées → 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>#ISO27701 #Privacy #ProtectionDesDonnées #RGPD #PECB #NigerCertify #Conformité</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
+          <t>Post CTA session</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
           <t>PROGRAMME</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
+      <c r="N67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68" ht="90" customHeight="1">
       <c r="A68" s="2" t="n">
         <v>12</v>
       </c>
@@ -4191,36 +4939,46 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Niger &amp; Sénégal — même session en ligne</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Certification internationale, accompagnement local. 94 10 70 74</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Post carrousel / texte</t>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>Niamey ↔ Dakar : une même session en ligne</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Que vous soyez au Niger ou au Sénégal, la session PECB est la même :
+• Exigence internationale
+• Accompagnement local NigerCertify
+• Démarrage 10 octobre 2026
+• 350 000 FCFA · 2 retakes
+Inscrivez-vous : WhatsApp 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>#Niger #Sénégal #PECB #FormationEnLigne #ISO27001 #NigerCertify #Certification</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
+          <t>Post texte / carrousel</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
+      <c r="N68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69" ht="90" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>12</v>
       </c>
@@ -4234,46 +4992,56 @@
           <t>Mar</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Parcours LPI : LE → LPIC-1 → LPIC-2 → LPIC-3</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Format mixte. LE 150 000 FCFA · LPIC 200 000 FCFA / niveau.</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Parcours LPI : de Linux Essentials à LPIC-3</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Admin Linux : un chemin clair avec NigerCertify.
+🐧 LPI LE (Linux Essentials) — 150 000 FCFA
+🐧 LPIC-1 · LPIC-2 · LPIC-3 — 200 000 FCFA / niveau
+📍 Format mixte (présentiel + en ligne)
+Progression : LE → LPIC-1 → LPIC-2 → LPIC-3
+Répondez LPI au 94 10 70 74 + votre niveau</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>#LPI #LPIC #Linux #LinuxEssentials #SysAdmin #NigerCertify #FormationLinux #OpenSource</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
         <is>
           <t>Post image + texte</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
+      <c r="N69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70" ht="90" customHeight="1">
       <c r="A70" s="2" t="n">
         <v>12</v>
       </c>
@@ -4297,37 +5065,49 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Session PECB 10 oct. 2026 — inscriptions ouvertes</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>ISO 27001 · ISO 27701 · en ligne · 12 mois · 2 retakes · 350 000 FCFA
-WhatsApp 94 10 70 74 — JE M’INSCRIS</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Session PECB — inscriptions ouvertes (10 oct. 2026)</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Les inscriptions sont ouvertes pour la session PECB NigerCertify.
+📅 Démarrage : 10 octobre 2026
+💻 100 % en ligne
+📘 ISO/IEC 27001 · ISO/IEC 27701
+⏱ Accès plateforme 12 mois
+🔁 2 retakes examens inclus
+💰 Tarif : 350 000 FCFA
+Niger &amp; Sénégal — certification internationale, accompagnement local.
+👉 WhatsApp 94 10 70 74 — écrivez JE M’INSCRIS</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>#PECB #ISO27001 #ISO27701 #Cybersécurité #Certification #NigerCertify #Niger #Sénégal #FormationEnLigne</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
         <is>
           <t>Post texte + CTA</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
+      <c r="J70" s="2" t="inlineStr">
         <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
+      <c r="N70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71" ht="90" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>12</v>
       </c>
@@ -4341,50 +5121,65 @@
           <t>Jeu</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>LPI</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>Linux Essentials — premier pas</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>TITRE : Linux Essentials — premier pas
-HOOK (0–5s) : Linux Essentials — premier pas
-CORPS : LPI LE · 150 000 FCFA · mixte. Idéal débutants &amp; reconversion.
-CTA fin : Écrivez LPI LE au 94 10 70 74
-DESCRIPTION : NigerCertify · Niger &amp; Sénégal · https://wa.me/22794107074?text=LPI%20LE</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Linux Essentials — le bon premier pas</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>TITRE VIDÉO : Linux Essentials — le bon premier pas
+HOOK (0–5 s) : Linux Essentials — le bon premier pas
+SCRIPT / CONTENU :
+Vous débutez sous Linux ou vous vous reconvertissez en IT ?
+LPI Linux Essentials (LPI LE) chez NigerCertify :
+• Bases système &amp; ligne de commande
+• Culture open source
+• Tarif : 150 000 FCFA
+• Format mixte
+Message LPI LE au 94 10 70 74
+CTA ÉCRAN DE FIN : Écrivez LPI LE au 94 10 70 74
+DESCRIPTION YOUTUBE :
+Vous débutez sous Linux ou vous vous reconvertissez en IT ?
+WhatsApp : https://wa.me/22794107074?text=LPI%20LE
+NigerCertify · Niger &amp; Sénégal</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>#LinuxEssentials #LPILE #Linux #ReconversionIT #Formation #NigerCertify #LPIC</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
         <is>
           <t>YouTube Short (45–60s)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>LPI LE</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
+      <c r="N71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72" ht="90" customHeight="1">
       <c r="A72" s="2" t="n">
         <v>12</v>
       </c>
@@ -4398,46 +5193,57 @@
           <t>Ven</t>
         </is>
       </c>
-      <c r="D72" s="9" t="inlineStr">
+      <c r="D72" s="10" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="E72" s="10" t="inlineStr">
+      <c r="E72" s="11" t="inlineStr">
         <is>
           <t>CouturePro</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>CouturePro — ateliers de couture</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Commandes, tissus, clients, délais — un seul outil.</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>CouturePro — le logiciel des ateliers de couture</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>Les ateliers perdent du temps sans suivi clair.
+CouturePro vous aide à gérer :
+• Commandes clients
+• Stocks tissus &amp; fournitures
+• Délais de livraison
+Un outil simple pour les couturiers et stylistes.
+Démo : écrivez COUTUREPRO au 94 10 70 74</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>#CouturePro #AtelierCouture #Mode #Artisanat #Digitalisation #NigerCertify #GestionAtelier</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t>Post / Reels</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>COUTUREPRO</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
+      <c r="N72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73" ht="90" customHeight="1">
       <c r="A73" s="2" t="n">
         <v>12</v>
       </c>
@@ -4461,39 +5267,50 @@
           <t>PECB</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>Pourquoi ISO 27001 ?</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Le langage commun de la sécurité de l’information. Session PECB NigerCertify dès le 10/10/2026.</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Statut / CTA session</t>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Pourquoi se certifier ISO 27001 ?</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>ISO 27001, c’est le langage commun de la sécurité de l’information.
+Avec NigerCertify, vous préparez votre certification PECB :
+• Session en ligne dès le 10 octobre 2026
+• Accès 12 mois + 2 retakes
+• Tarif : 350 000 FCFA
+Idéal pour RSSI, IT, consultants et équipes conformité.
+📩 Demandez le programme au 94 10 70 74 (mot-clé PROGRAMME)</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>#ISO27001 #PECB #SécuritéDeLInformation #SMSI #FormationIT #NigerCertify #AfriqueDeLOuest</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
+          <t>Post CTA session</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
           <t>PROGRAMME</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>À faire</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>À faire</t>
+        </is>
+      </c>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M73"/>
+  <autoFilter ref="A1:N73"/>
   <dataValidations count="3">
-    <dataValidation sqref="J2:J73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"À faire,En cours,Publié,Reporté"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -4513,14 +5330,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>Calendrier de publication NigerCertify</t>
         </is>
@@ -4543,77 +5360,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Répartition : PECB 60% · LPI 20% · nBusiness 15% · CouturePro 5%</t>
+          <t>Chaque publication contient : TITRE + CONTENU + HASHTAGS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Période : 12 semaines (colonne Date = jour de publication prévu)</t>
+          <t>Répartition : PECB 60% · LPI 20% · nBusiness 15% · CouturePro 5%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Légende des statuts</t>
+          <t>Colonnes clés</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>À faire / En cours / Publié / Reporté</t>
+          <t>Titre = accroche à afficher / titre YouTube</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Contenu = texte prêt à copier-coller (ou script YouTube)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Consignes</t>
+          <t>Hashtags = à coller en fin de post (Facebook/LinkedIn) ou dans la description YouTube</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1. Adapter le texte au format du canal (LinkedIn plus pro, Facebook plus local, YouTube = script + titre + description).</t>
+          <t>CTA = mot-clé WhatsApp</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2. Toujours finir par un CTA + WhatsApp 94 10 70 74.</t>
+          <t>Statut = À faire / En cours / Publié / Reporté</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3. Cocher Statut = Publié après mise en ligne ; coller l’URL dans Lien publication.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>4. YouTube : viser 3–8 min (tips) ou Shorts 30–60 s.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>5. Ne jamais publier de contenu lab offensif / exploit sur ces canaux.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>6. Jour type : Lun LinkedIn PECB · Mer Facebook mixte · Ven YouTube · Dim Facebook CTA.</t>
+          <t>Ne jamais publier de contenu lab offensif sur ces canaux.</t>
         </is>
       </c>
     </row>
@@ -4633,96 +5436,96 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Objectif mensuel (indicatif)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Canal</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Posts / mois (cible)</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>8–10</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>PECB + LPI B2B</t>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Chaque post = Titre + Contenu + Hashtags</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>10–12</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>PECB CTA + LPI + logiciels</t>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Coller Hashtags en fin de publication</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>4–6</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>Alterner tips PECB / Linux + 1 démo logiciel</t>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Titre = titre vidéo · Contenu = script · Hashtags = description</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>WhatsApp Status</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>20+</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Hors Excel mais quotidien</t>
         </is>
@@ -4750,213 +5553,213 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Grille tarifaire formations</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Offre</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Détail</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>Tarif (FCFA)</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>CTA</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>PECB ISO 27001/27701</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Session 10 oct. 2026 · 12 mois · 2 retakes</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>En ligne</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="16" t="n">
         <v>350000</v>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>JE M’INSCRIS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>LPI LE</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Linux Essentials</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Mixte</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="16" t="n">
         <v>150000</v>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>LPI LE</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>LPIC-1</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Linux Administrator</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Mixte</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="16" t="n">
         <v>200000</v>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>LPIC1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>LPIC-2</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Linux Engineer</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Mixte</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="16" t="n">
         <v>200000</v>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>LPIC2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>LPIC-3</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Linux Enterprise</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Mixte</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="16" t="n">
         <v>200000</v>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>LPIC3</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>nBusiness</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Gestion multi-secteur</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Démo</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Sur devis</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>NBUSINESS</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>CouturePro</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Ateliers couture</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Démo</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Sur devis</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>COUTUREPRO</t>
         </is>
